--- a/slab_detailer/IMPORTDXFNEW_output/IMPORTDXFNEW_bar_schedule.xlsx
+++ b/slab_detailer/IMPORTDXFNEW_output/IMPORTDXFNEW_bar_schedule.xlsx
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>5420</v>
+        <v>5400</v>
       </c>
       <c r="H33" t="n">
         <v>8</v>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>8Φ12x542/20</t>
+          <t>8Φ12x540/20</t>
         </is>
       </c>
     </row>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>2480</v>
+        <v>2500</v>
       </c>
       <c r="H49" t="n">
         <v>6</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>6Φ14x(164÷332)/20</t>
+          <t>6Φ14x(166÷334)/20</t>
         </is>
       </c>
     </row>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>3640</v>
+        <v>3660</v>
       </c>
       <c r="H54" t="n">
         <v>13</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>13Φ14x364/20</t>
+          <t>13Φ14x366/20</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>3640</v>
+        <v>3660</v>
       </c>
       <c r="H55" t="n">
         <v>7</v>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>7Φ14x364/20</t>
+          <t>7Φ14x366/20</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>5390</v>
+        <v>5370</v>
       </c>
       <c r="H77" t="n">
         <v>19</v>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>19Φ14x539/20</t>
+          <t>19Φ14x537/20</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>5390</v>
+        <v>5370</v>
       </c>
       <c r="H78" t="n">
         <v>7</v>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>7Φ14x539/20</t>
+          <t>7Φ14x537/20</t>
         </is>
       </c>
     </row>
